--- a/data/UntaggedBackwaterCaptures.xlsx
+++ b/data/UntaggedBackwaterCaptures.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\BackwaterGenetics\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C342EF24-C93A-4F38-B820-A4CD6EF7D2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05942BD-9B1C-4ABE-9EBC-B32F931129BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{367238B2-2575-4BDC-B0BE-0AEB4AF6CE82}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{367238B2-2575-4BDC-B0BE-0AEB4AF6CE82}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -179,12 +179,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -860,7 +858,7 @@
       <c r="C17" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>2</v>
       </c>
       <c r="E17" t="s">
@@ -880,7 +878,7 @@
       <c r="C18" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>10</v>
       </c>
       <c r="E18" t="s">
@@ -900,7 +898,7 @@
       <c r="C19" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>23</v>
       </c>
       <c r="E19" t="s">
@@ -957,7 +955,7 @@
       <c r="C22" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22">
         <v>9</v>
       </c>
       <c r="E22" t="s">
@@ -974,7 +972,7 @@
       <c r="C23" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23">
         <v>100</v>
       </c>
       <c r="E23" t="s">
@@ -991,7 +989,7 @@
       <c r="C24" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24">
         <v>531</v>
       </c>
       <c r="E24" t="s">
